--- a/template.xlsx
+++ b/template.xlsx
@@ -417,7 +417,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -689,55 +689,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
@@ -745,6 +701,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1858,30 +1817,18 @@
     <row r="21" ht="19.95" customHeight="1" s="77">
       <c r="B21" s="83" t="n"/>
       <c r="C21" s="85" t="n"/>
-      <c r="D21" s="97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 허가 기간 :</t>
-        </is>
-      </c>
-      <c r="E21" s="98" t="n"/>
-      <c r="F21" s="99" t="n"/>
-      <c r="G21" s="100" t="inlineStr">
-        <is>
-          <t>~</t>
-        </is>
-      </c>
-      <c r="H21" s="99" t="n"/>
-      <c r="I21" s="97" t="inlineStr">
-        <is>
-          <t>/   확인자 :</t>
-        </is>
-      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 허가 기간 :                             ~                              /   확인자 :                              (서명)</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="15" t="n"/>
+      <c r="H21" s="15" t="n"/>
+      <c r="I21" s="15" t="n"/>
       <c r="J21" s="15" t="n"/>
-      <c r="K21" s="97" t="inlineStr">
-        <is>
-          <t>(서명)</t>
-        </is>
-      </c>
+      <c r="K21" s="15" t="n"/>
       <c r="L21" s="15" t="n"/>
       <c r="M21" s="16" t="n"/>
     </row>
@@ -1934,28 +1881,9 @@
     <row r="25" ht="19.95" customHeight="1" s="77">
       <c r="B25" s="81" t="n"/>
       <c r="C25" s="82" t="n"/>
-      <c r="D25" s="101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 허가 기간 :</t>
-        </is>
-      </c>
-      <c r="E25" s="102" t="n"/>
-      <c r="F25" s="103" t="n"/>
-      <c r="G25" s="104" t="inlineStr">
-        <is>
-          <t>~</t>
-        </is>
-      </c>
-      <c r="H25" s="103" t="n"/>
-      <c r="I25" s="105" t="inlineStr">
-        <is>
-          <t>/   확인자 :</t>
-        </is>
-      </c>
-      <c r="J25" s="102" t="n"/>
-      <c r="K25" s="105" t="inlineStr">
-        <is>
-          <t>(서명)</t>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 허가 기간 :                             ~                              /   확인자 :                              (서명)</t>
         </is>
       </c>
       <c r="M25" s="23" t="n"/>
@@ -2007,30 +1935,18 @@
     <row r="28" ht="19.95" customHeight="1" s="77">
       <c r="B28" s="83" t="n"/>
       <c r="C28" s="85" t="n"/>
-      <c r="D28" s="106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 허가 기간 :</t>
-        </is>
-      </c>
-      <c r="E28" s="98" t="n"/>
-      <c r="F28" s="99" t="n"/>
-      <c r="G28" s="100" t="inlineStr">
-        <is>
-          <t>~</t>
-        </is>
-      </c>
-      <c r="H28" s="99" t="n"/>
-      <c r="I28" s="97" t="inlineStr">
-        <is>
-          <t>/   확인자 :</t>
-        </is>
-      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 허가 기간 :                             ~                              /   확인자 :                              (서명)</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="n"/>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="15" t="n"/>
+      <c r="H28" s="15" t="n"/>
+      <c r="I28" s="15" t="n"/>
       <c r="J28" s="15" t="n"/>
-      <c r="K28" s="97" t="inlineStr">
-        <is>
-          <t>(서명)</t>
-        </is>
-      </c>
+      <c r="K28" s="15" t="n"/>
       <c r="L28" s="15" t="n"/>
       <c r="M28" s="16" t="n"/>
     </row>
@@ -2063,30 +1979,18 @@
     <row r="30" ht="19.95" customHeight="1" s="77">
       <c r="B30" s="83" t="n"/>
       <c r="C30" s="85" t="n"/>
-      <c r="D30" s="106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 허가 기간 :</t>
-        </is>
-      </c>
-      <c r="E30" s="98" t="n"/>
-      <c r="F30" s="99" t="n"/>
-      <c r="G30" s="100" t="inlineStr">
-        <is>
-          <t>~</t>
-        </is>
-      </c>
-      <c r="H30" s="99" t="n"/>
-      <c r="I30" s="97" t="inlineStr">
-        <is>
-          <t>/   확인자 :</t>
-        </is>
-      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 허가 기간 :                             ~                              /   확인자 :                              (서명)</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="n"/>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="15" t="n"/>
+      <c r="H30" s="15" t="n"/>
+      <c r="I30" s="15" t="n"/>
       <c r="J30" s="15" t="n"/>
-      <c r="K30" s="97" t="inlineStr">
-        <is>
-          <t>(서명)</t>
-        </is>
-      </c>
+      <c r="K30" s="15" t="n"/>
       <c r="L30" s="15" t="n"/>
       <c r="M30" s="16" t="n"/>
     </row>
@@ -2128,27 +2032,15 @@
       <c r="F32" s="15" t="n"/>
       <c r="G32" s="15" t="n"/>
       <c r="H32" s="15" t="n"/>
-      <c r="I32" s="107" t="inlineStr">
-        <is>
-          <t>허가기간 :</t>
-        </is>
-      </c>
-      <c r="J32" s="108" t="inlineStr">
-        <is>
-          <t>~</t>
-        </is>
-      </c>
-      <c r="K32" s="97" t="inlineStr">
-        <is>
-          <t>확인자 :</t>
-        </is>
-      </c>
+      <c r="I32" s="97" t="inlineStr">
+        <is>
+          <t>허가기간 :               ~                 확인자 :               (서명)</t>
+        </is>
+      </c>
+      <c r="J32" s="15" t="n"/>
+      <c r="K32" s="15" t="n"/>
       <c r="L32" s="14" t="n"/>
-      <c r="M32" s="109" t="inlineStr">
-        <is>
-          <t>(서명)</t>
-        </is>
-      </c>
+      <c r="M32" s="16" t="n"/>
     </row>
     <row r="33" ht="19.95" customHeight="1" s="77">
       <c r="B33" s="44" t="inlineStr">
@@ -2161,19 +2053,15 @@
           <t>중장비</t>
         </is>
       </c>
-      <c r="D33" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 투입장비 : (</t>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 투입장비 : (                                                                           ) / 자격증 소지 □  ◯  /  현장책임 감독  □  ◯</t>
         </is>
       </c>
       <c r="E33" s="12" t="n"/>
-      <c r="F33" s="111" t="n"/>
-      <c r="G33" s="79" t="n"/>
-      <c r="H33" s="112" t="inlineStr">
-        <is>
-          <t>) / 자격증 소지 □  ◯  /  현장책임 감독  □  ◯</t>
-        </is>
-      </c>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="12" t="n"/>
+      <c r="H33" s="12" t="n"/>
       <c r="I33" s="12" t="n"/>
       <c r="J33" s="12" t="n"/>
       <c r="K33" s="12" t="n"/>
@@ -2193,30 +2081,18 @@
     <row r="35" ht="19.95" customHeight="1" s="77">
       <c r="B35" s="83" t="n"/>
       <c r="C35" s="85" t="n"/>
-      <c r="D35" s="106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 운전원 허가 기간 :</t>
-        </is>
-      </c>
-      <c r="E35" s="98" t="n"/>
-      <c r="F35" s="99" t="n"/>
-      <c r="G35" s="100" t="inlineStr">
-        <is>
-          <t>~</t>
-        </is>
-      </c>
-      <c r="H35" s="99" t="n"/>
-      <c r="I35" s="97" t="inlineStr">
-        <is>
-          <t>/   확인자 :</t>
-        </is>
-      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 운전원 허가 기간 :                             ~                              /   확인자 :                              (서명)</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="n"/>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="15" t="n"/>
+      <c r="H35" s="15" t="n"/>
+      <c r="I35" s="15" t="n"/>
       <c r="J35" s="15" t="n"/>
-      <c r="K35" s="97" t="inlineStr">
-        <is>
-          <t>(서명)</t>
-        </is>
-      </c>
+      <c r="K35" s="15" t="n"/>
       <c r="L35" s="15" t="n"/>
       <c r="M35" s="16" t="n"/>
     </row>
@@ -2320,7 +2196,7 @@
         </is>
       </c>
       <c r="C40" s="80" t="n"/>
-      <c r="D40" s="113" t="n"/>
+      <c r="D40" s="98" t="n"/>
       <c r="E40" s="79" t="n"/>
       <c r="F40" s="79" t="n"/>
       <c r="G40" s="79" t="n"/>
@@ -2448,48 +2324,24 @@
         </is>
       </c>
       <c r="C46" s="86" t="n"/>
-      <c r="D46" s="97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  20      년</t>
-        </is>
-      </c>
-      <c r="E46" s="114" t="inlineStr">
-        <is>
-          <t>월</t>
-        </is>
-      </c>
-      <c r="F46" s="114" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="G46" s="114" t="inlineStr">
-        <is>
-          <t>시부터</t>
-        </is>
-      </c>
-      <c r="H46" s="114" t="inlineStr">
-        <is>
-          <t>시까지</t>
-        </is>
-      </c>
-      <c r="I46" s="97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   담당자 :</t>
-        </is>
-      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  20      년            월            일            시부터             시까지       담당자 :                                                                 (서명)</t>
+        </is>
+      </c>
+      <c r="E46" s="15" t="n"/>
+      <c r="F46" s="15" t="n"/>
+      <c r="G46" s="15" t="n"/>
+      <c r="H46" s="15" t="n"/>
+      <c r="I46" s="15" t="n"/>
       <c r="J46" s="15" t="n"/>
       <c r="K46" s="15" t="n"/>
-      <c r="L46" s="97" t="inlineStr">
-        <is>
-          <t>(서명)</t>
-        </is>
-      </c>
+      <c r="L46" s="15" t="n"/>
       <c r="M46" s="16" t="n"/>
     </row>
     <row r="47" ht="19.95" customHeight="1" s="77"/>
   </sheetData>
-  <mergeCells count="67">
+  <mergeCells count="61">
     <mergeCell ref="K16:L16"/>
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="B7:C7"/>
@@ -2510,7 +2362,6 @@
     <mergeCell ref="B29:B30"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D21:E21"/>
     <mergeCell ref="K8:M8"/>
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="H6:I6"/>
@@ -2520,7 +2371,6 @@
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="G37:H37"/>
-    <mergeCell ref="F33:G33"/>
     <mergeCell ref="C31:C32"/>
     <mergeCell ref="C33:C35"/>
     <mergeCell ref="F9:H9"/>
@@ -2534,7 +2384,6 @@
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="C27:C28"/>
     <mergeCell ref="K6:L6"/>
-    <mergeCell ref="D28:E28"/>
     <mergeCell ref="B22:B26"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="I8:J8"/>
@@ -2548,14 +2397,11 @@
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="B17:E17"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D30:E30"/>
     <mergeCell ref="K9:M9"/>
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="C22:C26"/>
     <mergeCell ref="K18:L18"/>
     <mergeCell ref="I9:J9"/>
-    <mergeCell ref="D35:E35"/>
     <mergeCell ref="B31:B32"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2857,18 +2703,18 @@
         </is>
       </c>
       <c r="E8" s="80" t="n"/>
-      <c r="F8" s="115" t="n"/>
-      <c r="G8" s="116" t="n"/>
-      <c r="H8" s="117" t="n"/>
+      <c r="F8" s="99" t="n"/>
+      <c r="G8" s="100" t="n"/>
+      <c r="H8" s="101" t="n"/>
       <c r="I8" s="91" t="inlineStr">
         <is>
           <t>작업지역(장소)</t>
         </is>
       </c>
       <c r="J8" s="80" t="n"/>
-      <c r="K8" s="115" t="n"/>
-      <c r="L8" s="116" t="n"/>
-      <c r="M8" s="117" t="n"/>
+      <c r="K8" s="99" t="n"/>
+      <c r="L8" s="100" t="n"/>
+      <c r="M8" s="101" t="n"/>
     </row>
     <row r="9" ht="21" customHeight="1" s="77">
       <c r="B9" s="93" t="inlineStr">
@@ -2883,7 +2729,7 @@
         </is>
       </c>
       <c r="E9" s="85" t="n"/>
-      <c r="F9" s="118" t="n"/>
+      <c r="F9" s="102" t="n"/>
       <c r="G9" s="84" t="n"/>
       <c r="H9" s="84" t="n"/>
       <c r="I9" s="93" t="inlineStr">
@@ -2892,7 +2738,7 @@
         </is>
       </c>
       <c r="J9" s="85" t="n"/>
-      <c r="K9" s="99" t="n"/>
+      <c r="K9" s="103" t="n"/>
       <c r="L9" s="84" t="n"/>
       <c r="M9" s="85" t="n"/>
     </row>
@@ -3024,9 +2870,9 @@
           <t>작업구역 설정(출입경고 표지)</t>
         </is>
       </c>
-      <c r="C15" s="119" t="n"/>
-      <c r="D15" s="119" t="n"/>
-      <c r="E15" s="119" t="n"/>
+      <c r="C15" s="104" t="n"/>
+      <c r="D15" s="104" t="n"/>
+      <c r="E15" s="104" t="n"/>
       <c r="F15" s="32" t="inlineStr">
         <is>
           <t>□  ◯</t>
@@ -3037,8 +2883,8 @@
           <t>전원차단</t>
         </is>
       </c>
-      <c r="H15" s="119" t="n"/>
-      <c r="I15" s="119" t="n"/>
+      <c r="H15" s="104" t="n"/>
+      <c r="I15" s="104" t="n"/>
       <c r="J15" s="32" t="inlineStr">
         <is>
           <t>□  ◯</t>
@@ -3049,7 +2895,7 @@
           <t>감시자 배치</t>
         </is>
       </c>
-      <c r="L15" s="119" t="n"/>
+      <c r="L15" s="104" t="n"/>
       <c r="M15" s="32" t="inlineStr">
         <is>
           <t>□  ◯</t>
@@ -3276,7 +3122,7 @@
           <t xml:space="preserve">      지정하는 장소로 이동, 적치하여야 한다.</t>
         </is>
       </c>
-      <c r="I31" s="120" t="n"/>
+      <c r="I31" s="105" t="n"/>
       <c r="M31" s="23" t="n"/>
     </row>
     <row r="32" ht="21" customHeight="1" s="77">
@@ -3314,7 +3160,7 @@
         </is>
       </c>
       <c r="C34" s="80" t="n"/>
-      <c r="D34" s="121" t="inlineStr">
+      <c r="D34" s="106" t="inlineStr">
         <is>
           <t xml:space="preserve"> 1. 사내 외부인 출입시 반드시 경비실을 경유하여야 한다.</t>
         </is>
@@ -3338,7 +3184,7 @@
         </is>
       </c>
       <c r="G35" s="63" t="n"/>
-      <c r="L35" s="122" t="n"/>
+      <c r="L35" s="107" t="n"/>
       <c r="M35" s="82" t="n"/>
     </row>
     <row r="36" ht="21" customHeight="1" s="77">
@@ -3366,7 +3212,7 @@
         </is>
       </c>
       <c r="C37" s="80" t="n"/>
-      <c r="D37" s="113" t="n"/>
+      <c r="D37" s="98" t="n"/>
       <c r="E37" s="79" t="n"/>
       <c r="F37" s="79" t="n"/>
       <c r="G37" s="79" t="n"/>
@@ -3398,7 +3244,7 @@
       <c r="M39" s="85" t="n"/>
     </row>
     <row r="40" ht="21" customHeight="1" s="77">
-      <c r="B40" s="123" t="inlineStr">
+      <c r="B40" s="108" t="inlineStr">
         <is>
           <t>작업완료시간</t>
         </is>
@@ -3500,43 +3346,19 @@
         </is>
       </c>
       <c r="C44" s="86" t="n"/>
-      <c r="D44" s="97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  20      년</t>
-        </is>
-      </c>
-      <c r="E44" s="114" t="inlineStr">
-        <is>
-          <t>월</t>
-        </is>
-      </c>
-      <c r="F44" s="114" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="G44" s="114" t="inlineStr">
-        <is>
-          <t>시부터</t>
-        </is>
-      </c>
-      <c r="H44" s="114" t="inlineStr">
-        <is>
-          <t>시까지</t>
-        </is>
-      </c>
-      <c r="I44" s="97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   담당자 :</t>
-        </is>
-      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  20      년            월            일            시부터             시까지       담당자 :                                                                 (서명)</t>
+        </is>
+      </c>
+      <c r="E44" s="15" t="n"/>
+      <c r="F44" s="15" t="n"/>
+      <c r="G44" s="15" t="n"/>
+      <c r="H44" s="15" t="n"/>
+      <c r="I44" s="15" t="n"/>
       <c r="J44" s="15" t="n"/>
       <c r="K44" s="15" t="n"/>
-      <c r="L44" s="97" t="inlineStr">
-        <is>
-          <t>(서명)</t>
-        </is>
-      </c>
+      <c r="L44" s="15" t="n"/>
       <c r="M44" s="16" t="n"/>
     </row>
   </sheetData>
